--- a/Web Scraping/Project Assignments/project2.1 Companies _data_with_scarping.xlsx
+++ b/Web Scraping/Project Assignments/project2.1 Companies _data_with_scarping.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T460\web scraping\course-python-and-automation-by-kasi\Web Scraping\Project Assignments\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>main_link</t>
   </si>
@@ -34,9 +29,6 @@
   </si>
   <si>
     <t>Contact number</t>
-  </si>
-  <si>
-    <t>Website address</t>
   </si>
   <si>
     <t>Establishment year</t>
@@ -45,8 +37,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,17 +391,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="7" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="25.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,11 +417,8 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
